--- a/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
+++ b/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
@@ -83,7 +83,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603</t>
+          <t xml:space="preserve">605</t>
         </is>
       </c>
     </row>
@@ -95,7 +95,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
     </row>
@@ -107,7 +107,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
     </row>
@@ -131,7 +131,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
     </row>
@@ -155,7 +155,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
     </row>
@@ -3547,47 +3547,47 @@
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Protection</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.080 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3597,24 +3597,24 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-026</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">PARTIAL</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+          <t xml:space="preserve">Local PlantControlV2 exact equation and supplemental RAW observations; data/current_v8/st_power_evidence_20260924.json</t>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT trip command timing</t>
+          <t xml:space="preserve">52GT breaker open timing</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3634,17 +3634,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active</t>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.055 s</t>
+          <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-025</t>
+          <t xml:space="preserve">IG-026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -3674,24 +3674,24 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Protection</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52GT trip command timing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-025</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -3741,79 +3741,146 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST Protection</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M55"/>
 </worksheet>
 </file>
 
@@ -7070,7 +7137,7 @@
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -7085,7 +7152,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7097,7 +7164,7 @@
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -7112,7 +7179,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -7124,7 +7191,7 @@
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -7139,7 +7206,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7151,7 +7218,7 @@
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -7178,22 +7245,22 @@
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT-01</t>
+          <t xml:space="preserve">IN-02</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7205,22 +7272,22 @@
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-01</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7232,12 +7299,12 @@
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-02</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7247,7 +7314,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7259,7 +7326,7 @@
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -7274,7 +7341,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7286,7 +7353,7 @@
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -7313,32 +7380,113 @@
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN-02</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUT</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUT-01</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUTPUT</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="44" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN-01</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUT</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="44" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E130"/>
+  <autoFilter ref="A1:E133"/>
 </worksheet>
 </file>
 
@@ -13623,12 +13771,12 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -13638,7 +13786,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -13665,471 +13813,598 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPERATION</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST grid power response after 52ST opens
+PHYSICAL_RESPONSE</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="44" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">additional:RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL_INFO</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL INFO</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">immediate model relation</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="44" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="44" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52GT breaker open timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="44" customHeight="1">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="44" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="44" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="155" ht="44" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="44" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="44" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52GT trip command timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="44" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="44" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="44" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="158" ht="44" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="44" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="44" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST breaker open timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="44" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="44" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.100 s</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="44" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="161" ht="44" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="44" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="44" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="44" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="44" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H160"/>
+  <autoFilter ref="A1:H163"/>
 </worksheet>
 </file>
 
@@ -17863,7 +18138,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -17873,7 +18148,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -17885,7 +18160,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -17895,7 +18170,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -17907,17 +18182,17 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -17929,12 +18204,12 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -17951,7 +18226,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -17961,7 +18236,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -17973,83 +18248,83 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">PORT:IN-02</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
+          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-02</t>
+          <t xml:space="preserve">PORT:IN-01</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -18061,17 +18336,17 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -18083,12 +18358,12 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -18105,7 +18380,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -18115,7 +18390,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -18127,48 +18402,136 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">PORT:IN-02</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="44" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORT:OUT-01</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUTPUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="44" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORT:IN-01</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="44" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="44" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D183"/>
+  <autoFilter ref="A1:D187"/>
 </worksheet>
 </file>
--- a/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
+++ b/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
@@ -83,7 +83,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603</t>
+          <t xml:space="preserve">604</t>
         </is>
       </c>
     </row>
@@ -95,7 +95,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
     </row>
@@ -107,7 +107,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
     </row>
@@ -131,7 +131,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
@@ -155,7 +155,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
     </row>
@@ -3547,47 +3547,47 @@
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Protection</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.080 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3597,24 +3597,24 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-026</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">PARTIAL</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+          <t xml:space="preserve">Exact Modelica equation + private local RAW readback hash; behavior verification remains PARTIAL</t>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT trip command timing</t>
+          <t xml:space="preserve">52GT breaker open timing</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3634,17 +3634,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active</t>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.055 s</t>
+          <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-025</t>
+          <t xml:space="preserve">IG-026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -3674,24 +3674,24 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Protection</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52GT trip command timing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-025</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -3741,79 +3741,146 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST Protection</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M55"/>
 </worksheet>
 </file>
 
@@ -7070,7 +7137,7 @@
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -7085,7 +7152,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7097,22 +7164,22 @@
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-02</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -7129,17 +7196,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT-01</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7151,12 +7218,12 @@
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-01</t>
+          <t xml:space="preserve">IN-02</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7166,7 +7233,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7178,7 +7245,7 @@
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -7193,7 +7260,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7205,7 +7272,7 @@
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -7220,7 +7287,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7232,22 +7299,22 @@
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-02</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7264,17 +7331,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT-01</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7286,12 +7353,12 @@
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-01</t>
+          <t xml:space="preserve">IN-02</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7301,7 +7368,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
+          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7313,32 +7380,86 @@
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUT-01</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUTPUT</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN-01</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUT</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="44" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E130"/>
+  <autoFilter ref="A1:E132"/>
 </worksheet>
 </file>
 
@@ -13623,12 +13744,12 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -13638,7 +13759,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -13665,471 +13786,598 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPERATION</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST grid power response after 52ST opens
+PHYSICAL_RESPONSE</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="44" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">additional:RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL_INFO</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL INFO</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">immediate model relation</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="44" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="44" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52GT breaker open timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="44" customHeight="1">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="44" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="44" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="155" ht="44" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="44" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="44" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52GT trip command timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="44" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="44" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="44" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="158" ht="44" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="44" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="44" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST breaker open timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="44" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="44" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.100 s</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="44" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="161" ht="44" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="44" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="44" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="44" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="44" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H160"/>
+  <autoFilter ref="A1:H163"/>
 </worksheet>
 </file>
 
@@ -17863,7 +18111,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -17873,7 +18121,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -17885,44 +18133,44 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-02</t>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -17934,34 +18182,34 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">PORT:IN-01</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">PORT:IN-02</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -17973,17 +18221,17 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -17995,12 +18243,12 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -18017,7 +18265,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -18027,7 +18275,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -18039,44 +18287,44 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-02</t>
+          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -18088,34 +18336,34 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">PORT:IN-01</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
+          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">PORT:IN-02</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -18127,17 +18375,17 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -18149,26 +18397,92 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORT:OUT-01</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUTPUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="44" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORT:IN-01</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="44" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="44" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D183"/>
+  <autoFilter ref="A1:D186"/>
 </worksheet>
 </file>
--- a/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
+++ b/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
@@ -83,96 +83,168 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">live_tags</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">input_groups</t>
+          <t xml:space="preserve">searchable_tags</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">605</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">equipment_pages</t>
+          <t xml:space="preserve">model_source_raw_observed_tags</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pages</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_inputs</t>
+          <t xml:space="preserve">live_rules</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_outputs</t>
+          <t xml:space="preserve">source_mapped_rules</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">input_groups</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">live_input_groups</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equipment_pages</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pages</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_inputs</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_outputs</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">derived_outputs</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>
 
@@ -192,6 +264,15 @@
     <col min="11" max="11" width="38" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="38" customWidth="1"/>
+    <col min="14" max="14" width="38" customWidth="1"/>
+    <col min="15" max="15" width="38" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -260,6 +341,51 @@
           <t xml:space="preserve">source_basis</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_kind</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_mapped</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runtime_inclusion</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model_source_status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_session_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_rows</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_closed_samples</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_open_samples</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open_behavior_test_status</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -327,6 +453,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -394,6 +565,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -461,6 +677,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -528,6 +789,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -595,6 +901,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -662,6 +1013,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -729,6 +1125,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -796,6 +1237,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -863,6 +1349,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -930,6 +1461,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -997,6 +1573,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1064,6 +1685,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1131,6 +1797,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1198,6 +1909,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1265,6 +2021,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1332,6 +2133,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1399,6 +2245,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1466,6 +2357,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1533,6 +2469,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -1600,6 +2581,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1667,6 +2693,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -1734,6 +2805,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1801,6 +2917,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1868,6 +3029,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1935,6 +3141,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2002,6 +3253,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2069,6 +3365,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -2136,6 +3477,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2203,6 +3589,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -2270,6 +3701,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2337,6 +3813,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -2404,6 +3925,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2471,6 +4037,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -2538,6 +4149,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2605,6 +4261,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -2672,6 +4373,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -2739,6 +4485,51 @@
           <t xml:space="preserve">Exact expression recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -2806,6 +4597,51 @@
           <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2873,6 +4709,51 @@
           <t xml:space="preserve">Exact GT request equation recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -2940,6 +4821,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -3007,6 +4933,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -3074,6 +5045,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3141,6 +5157,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -3208,6 +5269,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -3275,6 +5381,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -3342,6 +5493,51 @@
           <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -3409,6 +5605,51 @@
           <t xml:space="preserve">9-cause common-trip matrix + RAW nodes</t>
         </is>
       </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -3476,6 +5717,51 @@
           <t xml:space="preserve">Exact model equation</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -3543,6 +5829,51 @@
           <t xml:space="preserve">Exact model equation</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -3567,12 +5898,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
+          <t xml:space="preserve">vppSTGeneratorPowerMW | vpp52STClosed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
+          <t xml:space="preserve">vppSTGridPowerMW = if not vpp52STClosed then 0 else vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3607,7 +5938,52 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local PlantControlV2 exact equation and supplemental RAW observations; data/current_v8/st_power_evidence_20260924.json</t>
+          <t xml:space="preserve">Model source modelica/TripLens_CombinedCycle_TripTAC_ProcessView_v36.mo lines 1136-1137 (cd454995656af9a8747efe8930d2aa0b92f98e1083acadc858eaa7959ea6d2c5); RAW RAW_SESSION_20260924_191347.csv (055f8a21b8f586feafaa6fe6705cfca05b4f1e833713991a0cac1f0e94ad6fd9).</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_SESSION_OBSERVED_CLOSED_ONLY</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_TESTED</t>
         </is>
       </c>
     </row>
@@ -3677,6 +6053,51 @@
           <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -3744,6 +6165,51 @@
           <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
         </is>
       </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -3811,6 +6277,51 @@
           <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -3878,9 +6389,54 @@
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:V55"/>
 </worksheet>
 </file>
 
@@ -7152,12 +9708,12 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAW_NODE</t>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
         </is>
       </c>
     </row>
@@ -7179,7 +9735,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTGeneratorPowerMW</t>
+          <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -7211,7 +9767,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAW_NODE</t>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
         </is>
       </c>
     </row>
@@ -13786,7 +16342,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
+          <t xml:space="preserve">vppSTGridPowerMW = if not vpp52STClosed then 0 else vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">

--- a/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
+++ b/generated/logic/09_LOGIC_DEFINITION_MASTER_CURRENT_V8.xlsx
@@ -83,96 +83,168 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">604</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">live_tags</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">input_groups</t>
+          <t xml:space="preserve">searchable_tags</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">606</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">equipment_pages</t>
+          <t xml:space="preserve">model_source_raw_observed_tags</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pages</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_inputs</t>
+          <t xml:space="preserve">live_rules</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_outputs</t>
+          <t xml:space="preserve">source_mapped_rules</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">input_groups</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">live_input_groups</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equipment_pages</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pages</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_inputs</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_outputs</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">derived_outputs</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>
 
@@ -192,6 +264,15 @@
     <col min="11" max="11" width="38" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="38" customWidth="1"/>
+    <col min="14" max="14" width="38" customWidth="1"/>
+    <col min="15" max="15" width="38" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -260,6 +341,51 @@
           <t xml:space="preserve">source_basis</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_kind</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_mapped</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runtime_inclusion</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model_source_status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_session_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_rows</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_closed_samples</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_open_samples</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open_behavior_test_status</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -327,6 +453,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -394,6 +565,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -461,6 +677,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -528,6 +789,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -595,6 +901,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -662,6 +1013,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -729,6 +1125,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -796,6 +1237,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -863,6 +1349,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -930,6 +1461,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -997,6 +1573,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1064,6 +1685,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1131,6 +1797,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1198,6 +1909,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1265,6 +2021,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1332,6 +2133,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1399,6 +2245,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1466,6 +2357,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1533,6 +2469,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -1600,6 +2581,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1667,6 +2693,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -1734,6 +2805,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1801,6 +2917,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1868,6 +3029,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1935,6 +3141,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2002,6 +3253,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2069,6 +3365,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -2136,6 +3477,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2203,6 +3589,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -2270,6 +3701,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2337,6 +3813,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -2404,6 +3925,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2471,6 +4037,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -2538,6 +4149,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2605,6 +4261,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -2672,6 +4373,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -2739,6 +4485,51 @@
           <t xml:space="preserve">Exact expression recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -2806,6 +4597,51 @@
           <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2873,6 +4709,51 @@
           <t xml:space="preserve">Exact GT request equation recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -2940,6 +4821,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -3007,6 +4933,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -3074,6 +5045,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3141,6 +5157,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -3208,6 +5269,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -3275,11 +5381,56 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3289,22 +5440,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST trip latch</t>
+          <t xml:space="preserve">52ST breaker open protection cause</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LATCH</t>
+          <t xml:space="preserve">PROTECTION_CAUSE</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripRequest | vppSTTripResetNative</t>
+          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">request=1 AND reset&lt;0.5 -&gt; latch; reset clears</t>
+          <t xml:space="preserve">52ST close command &lt; 0.5 -&gt; breaker-open cause latch</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -3314,12 +5465,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reset input</t>
+          <t xml:space="preserve">ST reset with active trip causes clear and 52ST command open</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
+          <t xml:space="preserve">vppCauseSTBreakerOpenWhileRunning</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3329,7 +5480,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-024</t>
+          <t xml:space="preserve">IG-037</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3339,14 +5490,59 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
+          <t xml:space="preserve">TRIPLENS_ST_BREAKER_OPEN_TRIP_V1; 2026-09-26 PlantControlV2 build 104046 runtime proof</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_RUNTIME_VERIFIED</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUNTIME_VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3356,37 +5552,37 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST trip request common-trip matrix</t>
+          <t xml:space="preserve">ST trip latch</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRIP_REQUEST</t>
+          <t xml:space="preserve">LATCH</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseDirectGTTrip | vppCauseDirectSTTrip | vppCauseGTBreakerOpenWhileRunning | vppCauseHPDrumHH | vppCauseIPDrumHH | vppCauseLPDrumHH | vppCauseHPDrumLL | vppCauseIPDrumLL | vppCauseLPDrumLL</t>
+          <t xml:space="preserve">vppSTTripRequest | vppSTTripResetNative</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OR(all 9 causes)</t>
+          <t xml:space="preserve">request=1 AND reset&lt;0.5 -&gt; latch; reset clears</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 s</t>
+          <t xml:space="preserve">event-driven</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST reset</t>
+          <t xml:space="preserve">reset input</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripRequest</t>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3396,7 +5592,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-022</t>
+          <t xml:space="preserve">IG-024</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -3406,54 +5602,99 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-cause common-trip matrix + RAW nodes</t>
+          <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-GT-POWER</t>
+          <t xml:space="preserve">PROT-ST-REQUEST</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Response</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT power response after breaker open</t>
+          <t xml:space="preserve">ST trip request</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
+          <t xml:space="preserve">TRIP_REQUEST</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppGTTripRequest | vppCauseDirectSTTrip | vppCauseSTBreakerOpenWhileRunning | vppCauseHPDrumHH | vppCauseIPDrumHH | vppCauseLPDrumHH</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52GT not closed then GT generator power = 0</t>
+          <t xml:space="preserve">OR(registered ST trip inputs)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">immediate model relation</t>
+          <t xml:space="preserve">0 s</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">ST reset</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTGPowerMW</t>
+          <t xml:space="preserve">vppSTTripRequest</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3463,7 +5704,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-029</t>
+          <t xml:space="preserve">IG-022</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -3473,14 +5714,59 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exact model equation</t>
+          <t xml:space="preserve">Current PlantControlV2 ST request equation; cause-count wording retired; 52ST breaker-open cause included.</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-GT-SPEED</t>
+          <t xml:space="preserve">RESP-GT-POWER</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3490,7 +5776,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT speed coastdown after breaker open</t>
+          <t xml:space="preserve">GT power response after breaker open</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3505,12 +5791,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52GT opens, speed decays from nominal by coastdown model</t>
+          <t xml:space="preserve">if 52GT not closed then GT generator power = 0</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dynamic</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3520,7 +5806,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTGSpeedRPM</t>
+          <t xml:space="preserve">vppGTGPowerMW</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,23 +5827,68 @@
       <c r="M50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Exact model equation</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+          <t xml:space="preserve">RESP-GT-SPEED</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Response</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST grid power response after 52ST opens</t>
+          <t xml:space="preserve">GT speed coastdown after breaker open</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3567,27 +5898,27 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
+          <t xml:space="preserve">if 52GT opens, speed decays from nominal by coastdown model</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">immediate model relation</t>
+          <t xml:space="preserve">dynamic</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">follows 52ST closed feedback</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTGridPowerMW</t>
+          <t xml:space="preserve">vppGTGSpeedRPM</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3597,64 +5928,109 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-036</t>
+          <t xml:space="preserve">IG-029</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL</t>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exact Modelica equation + private local RAW readback hash; behavior verification remains PARTIAL</t>
+          <t xml:space="preserve">Exact model equation</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Protection</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vppSTGeneratorPowerMW | vpp52STClosed</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">vppSTGridPowerMW = if not vpp52STClosed then 0 else vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.080 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3664,7 +6040,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-026</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -3674,14 +6050,59 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+          <t xml:space="preserve">Model source modelica/TripLens_CombinedCycle_TripTAC_ProcessView_v36.mo lines 1136-1137 (cd454995656af9a8747efe8930d2aa0b92f98e1083acadc858eaa7959ea6d2c5); RAW RAW_SESSION_20260924_191347.csv (055f8a21b8f586feafaa6fe6705cfca05b4f1e833713991a0cac1f0e94ad6fd9).; 2026-09-26 PlantControlV2 104046 runtime proof verified 52ST OPEN -&gt; vppSTGridPowerMW = 0 MW.</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_RUNTIME_VERIFIED</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUNTIME_VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3691,7 +6112,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT trip command timing</t>
+          <t xml:space="preserve">52GT breaker open timing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3701,17 +6122,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active</t>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.055 s</t>
+          <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3721,7 +6142,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3731,7 +6152,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-025</t>
+          <t xml:space="preserve">IG-026</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -3741,24 +6162,69 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Protection</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52GT trip command timing</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3768,17 +6234,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3788,7 +6254,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3798,7 +6264,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-025</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -3808,79 +6274,281 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST Protection</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:V56"/>
 </worksheet>
 </file>
 
@@ -6678,7 +9346,7 @@
     <row r="104" ht="44" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6693,7 +9361,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripRequest</t>
+          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6705,27 +9373,27 @@
     <row r="105" ht="44" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-02</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripResetNative</t>
+          <t xml:space="preserve">vppCauseSTBreakerOpenWhileRunning</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAW_NODE</t>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
         </is>
       </c>
     </row>
@@ -6737,17 +9405,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT-01</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
+          <t xml:space="preserve">vppSTTripRequest</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6759,12 +9427,12 @@
     <row r="107" ht="44" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-01</t>
+          <t xml:space="preserve">IN-02</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6774,7 +9442,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseDirectGTTrip</t>
+          <t xml:space="preserve">vppSTTripResetNative</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6786,22 +9454,22 @@
     <row r="108" ht="44" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-02</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseDirectSTTrip</t>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6818,7 +9486,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-03</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6828,7 +9496,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseGTBreakerOpenWhileRunning</t>
+          <t xml:space="preserve">vppGTTripRequest</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6845,7 +9513,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-04</t>
+          <t xml:space="preserve">IN-02</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6855,7 +9523,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseHPDrumHH</t>
+          <t xml:space="preserve">vppCauseDirectSTTrip</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6872,7 +9540,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-05</t>
+          <t xml:space="preserve">IN-03</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6882,12 +9550,12 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseIPDrumHH</t>
+          <t xml:space="preserve">vppCauseSTBreakerOpenWhileRunning</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAW_NODE</t>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
         </is>
       </c>
     </row>
@@ -6899,7 +9567,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-06</t>
+          <t xml:space="preserve">IN-04</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6909,7 +9577,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseLPDrumHH</t>
+          <t xml:space="preserve">vppCauseHPDrumHH</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6926,7 +9594,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-07</t>
+          <t xml:space="preserve">IN-05</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6936,7 +9604,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseHPDrumLL</t>
+          <t xml:space="preserve">vppCauseIPDrumHH</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6953,7 +9621,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-08</t>
+          <t xml:space="preserve">IN-06</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6963,7 +9631,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseIPDrumLL</t>
+          <t xml:space="preserve">vppCauseLPDrumHH</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6980,17 +9648,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-09</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseLPDrumLL</t>
+          <t xml:space="preserve">vppSTTripRequest</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -7002,22 +9670,22 @@
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">RESP-GT-POWER</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT-01</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripRequest</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -7034,17 +9702,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-01</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppGTGPowerMW</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7056,22 +9724,22 @@
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-GT-POWER</t>
+          <t xml:space="preserve">RESP-GT-SPEED</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT-01</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTGPowerMW</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -7088,17 +9756,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-01</t>
+          <t xml:space="preserve">OUT-01</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppGTGSpeedRPM</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -7110,27 +9778,27 @@
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-GT-SPEED</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT-01</t>
+          <t xml:space="preserve">IN-01</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTGSpeedRPM</t>
+          <t xml:space="preserve">vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAW_NODE</t>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
         </is>
       </c>
     </row>
@@ -7142,7 +9810,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN-01</t>
+          <t xml:space="preserve">IN-02</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -7184,7 +9852,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAW_NODE</t>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
         </is>
       </c>
     </row>
@@ -13236,12 +15904,12 @@
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
+          <t xml:space="preserve">condition:PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -13251,7 +15919,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">request=1 AND reset&lt;0.5 -&gt; latch; reset clears</t>
+          <t xml:space="preserve">52ST close command &lt; 0.5 -&gt; breaker-open cause latch</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -13278,152 +15946,152 @@
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:PROT-ST-BRK-OPEN</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPERATION</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open protection cause
+PROTECTION_CAUSE</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="44" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">additional:PROT-ST-BRK-OPEN</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL_INFO</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL INFO</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event-driven</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST reset with active trip causes clear and 52ST command open</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="44" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">request=1 AND reset&lt;0.5 -&gt; latch; reset clears</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="44" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:PROT-ST-LATCH</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST trip latch
 LATCH</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="44" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">additional:PROT-ST-LATCH</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADDITIONAL_INFO</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADDITIONAL INFO</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event-driven</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reset input</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PASS</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RAW_NODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="44" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">condition:PROT-ST-REQUEST</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONDITION</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OR(all 9 causes)</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="44" customHeight="1">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">operation:PROT-ST-REQUEST</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPERATION</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ST trip request common-trip matrix
-TRIP_REQUEST</t>
-        </is>
-      </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -13448,12 +16116,12 @@
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">additional:PROT-ST-REQUEST</t>
+          <t xml:space="preserve">additional:PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -13468,12 +16136,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 s</t>
+          <t xml:space="preserve">event-driven</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST reset</t>
+          <t xml:space="preserve">reset input</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -13490,12 +16158,12 @@
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-GT-POWER</t>
+          <t xml:space="preserve">PROT-ST-REQUEST</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:RESP-GT-POWER</t>
+          <t xml:space="preserve">condition:PROT-ST-REQUEST</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -13505,7 +16173,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52GT not closed then GT generator power = 0</t>
+          <t xml:space="preserve">OR(registered ST trip inputs)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -13532,852 +16200,979 @@
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PROT-ST-REQUEST</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:PROT-ST-REQUEST</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPERATION</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST trip request
+TRIP_REQUEST</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="44" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROT-ST-REQUEST</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">additional:PROT-ST-REQUEST</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL_INFO</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADDITIONAL INFO</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 s</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST reset</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="44" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">RESP-GT-POWER</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition:RESP-GT-POWER</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">if 52GT not closed then GT generator power = 0</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="44" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESP-GT-POWER</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:RESP-GT-POWER</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GT power response after breaker open
 PHYSICAL_RESPONSE</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="44" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="44" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RESP-GT-POWER</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:RESP-GT-POWER</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="44" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="149" ht="44" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RESP-GT-SPEED</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:RESP-GT-SPEED</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">if 52GT opens, speed decays from nominal by coastdown model</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="44" customHeight="1">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="44" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RESP-GT-SPEED</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:RESP-GT-SPEED</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GT speed coastdown after breaker open
 PHYSICAL_RESPONSE</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="44" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="44" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RESP-GT-SPEED</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:RESP-GT-SPEED</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">dynamic</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="44" customHeight="1">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="152" ht="44" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="44" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTGridPowerMW = if not vpp52STClosed then 0 else vppSTGeneratorPowerMW</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="44" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST grid power response after 52ST opens
 PHYSICAL_RESPONSE</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="44" customHeight="1">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="44" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARTIAL</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="44" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="155" ht="44" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="44" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="44" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52GT breaker open timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="44" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="44" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="44" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="158" ht="44" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="44" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="44" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52GT trip command timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="44" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="44" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="44" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="161" ht="44" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="44" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="44" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST breaker open timing
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="44" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="44" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0.100 s</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="44" customHeight="1">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="164" ht="44" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="44" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="44" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATION</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command
 BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="44" customHeight="1">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="44" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">additional:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL_INFO</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDITIONAL INFO</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H163"/>
+  <autoFilter ref="A1:H166"/>
 </worksheet>
 </file>
 
@@ -17649,7 +20444,7 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -17659,7 +20454,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
+          <t xml:space="preserve">condition:PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -17671,44 +20466,44 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-02</t>
+          <t xml:space="preserve">condition:PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
+          <t xml:space="preserve">operation:PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
+          <t xml:space="preserve">operation:PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:PROT-ST-LATCH</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -17720,34 +20515,34 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">operation:PROT-ST-LATCH</t>
+          <t xml:space="preserve">PORT:IN-01</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
+          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">PORT:IN-02</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:PROT-ST-REQUEST</t>
+          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -17759,44 +20554,44 @@
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-02</t>
+          <t xml:space="preserve">condition:PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:PROT-ST-REQUEST</t>
+          <t xml:space="preserve">operation:PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-03</t>
+          <t xml:space="preserve">operation:PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -17808,7 +20603,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-04</t>
+          <t xml:space="preserve">PORT:IN-01</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -17830,7 +20625,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-05</t>
+          <t xml:space="preserve">PORT:IN-02</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -17852,7 +20647,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-06</t>
+          <t xml:space="preserve">PORT:IN-03</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -17874,7 +20669,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-07</t>
+          <t xml:space="preserve">PORT:IN-04</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -17896,7 +20691,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-08</t>
+          <t xml:space="preserve">PORT:IN-05</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -17918,7 +20713,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-09</t>
+          <t xml:space="preserve">PORT:IN-06</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -18138,17 +20933,17 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PORT:IN-02</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
-        </is>
-      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
@@ -18160,39 +20955,39 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">condition:RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
-        </is>
-      </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">operation:RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -18204,7 +20999,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-02</t>
+          <t xml:space="preserve">PORT:IN-01</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -18226,17 +21021,17 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PORT:IN-02</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
-        </is>
-      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
@@ -18248,39 +21043,39 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">condition:SEQ-52GT-OPEN</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
-        </is>
-      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">operation:SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -18292,17 +21087,17 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PORT:IN-01</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
-        </is>
-      </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
@@ -18314,39 +21109,39 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">condition:SEQ-52GT-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
-        </is>
-      </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">operation:SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -18358,7 +21153,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-02</t>
+          <t xml:space="preserve">PORT:IN-01</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -18380,17 +21175,17 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PORT:IN-02</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
-        </is>
-      </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
@@ -18402,39 +21197,39 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">condition:SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PORT:OUT-01</t>
-        </is>
-      </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUTPUT</t>
+          <t xml:space="preserve">CONDITION</t>
         </is>
       </c>
     </row>
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORT:IN-01</t>
+          <t xml:space="preserve">operation:SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+          <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INPUT</t>
+          <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
@@ -18446,17 +21241,17 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PORT:IN-01</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
-        </is>
-      </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONDITION</t>
+          <t xml:space="preserve">INPUT</t>
         </is>
       </c>
     </row>
@@ -18468,21 +21263,43 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">condition:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="44" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operation:SEQ-52ST-TRIPCMD</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PORT:OUT-01</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OUTPUT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D186"/>
+  <autoFilter ref="A1:D187"/>
 </worksheet>
 </file>